--- a/filledforms/students.xlsx
+++ b/filledforms/students.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="20">
   <si>
     <t>Name</t>
   </si>
@@ -25,13 +25,52 @@
     <t>Semester</t>
   </si>
   <si>
-    <t>SHYAMSUNDAR SS</t>
-  </si>
-  <si>
-    <t>2303717673821040</t>
+    <t>Profile Image</t>
+  </si>
+  <si>
+    <t>Shyamsundar SS</t>
+  </si>
+  <si>
+    <t>2345678765432</t>
   </si>
   <si>
     <t>M.Sc Data Science</t>
+  </si>
+  <si>
+    <t>sundarshyam SS</t>
+  </si>
+  <si>
+    <t>TestStudent</t>
+  </si>
+  <si>
+    <t>99999999</t>
+  </si>
+  <si>
+    <t>MCA</t>
+  </si>
+  <si>
+    <t>jothisri SS</t>
+  </si>
+  <si>
+    <t>VerificationStudent</t>
+  </si>
+  <si>
+    <t>88888888</t>
+  </si>
+  <si>
+    <t>srijothi SS</t>
+  </si>
+  <si>
+    <t>data:image/jpeg;base64,/9j/4AAQSkZJRgABAQAAAQABAAD/2wCEAAkGBwgHBgkIBwgKCgkLDRYPDQwMDRsUFRAWIB0iIiAdHx8kKDQsJCYxJx8fLT0tMTU3Ojo6Iys/RD84QzQ5OjcBCgoKDQwNGg8PGjclHyU3Nzc3Nzc3Nzc3Nzc3Nzc3Nzc3Nzc3Nzc3Nzc3Nzc3Nzc3Nzc3Nzc3Nzc3Nzc3Nzc3N//AABEIAJQAlAMBIgACEQEDEQH/xAAcAAABBAMBAAAAAAAAAAAAAAAGAAQFBwIDCAH/xABHEAACAQMDAgMEBgYGBwkAAAABAgMABBEFEiEGMRNBUQciYZEUMkJxgaEjM1JiscEIFSTR0vAWQ3KCssLiF0RTZHSSoqPh/8QAGQEAAwEBAQAAAAAAAAAAAAAAAAECAwQF/8QAJREAAgMAAgEEAQUAAAAAAAAAAAECAxESITEEExRBYSIyM1Fx/9oADAMBAAIRAxEAPwAG1G9BUqD3oekbc5NOrk7nIPNNmXg00xtGIrNDg15GmRWwJikxIyZuKVnZTalqFvZW6lpZ5AigDPfz VanyD3qR6Z8dNfsJLadopRKPfTuFx72PiVyKl9Ird6LN1KSDT9FtLMagBNZw FJ4eSSRjAAOPOhO917UYbdRcW8LbT9eWPPJ 80/kur27imu1t2RRlgGAYgknnOO/PfP4UL6pNcXUaNdSFUDFFjHc45z defGKb1nS3nQwnu5dSud87A gHAHyqc0XRZboHbEc5744xWOg6fbuQX95PTbyfvo8s1dEZLW3kZUj3bIwAcegJ/wA8UWWZ0jaqvWRuj6BNDeCeeFX2MNuW4/EedF2t20s j3DaXHBbagyF0ZIxtdh3z6Hjg XFRKXrF0Qh0AXdh/rDnHz8qntMDuVyMAnI7/nXPGffZvKtNFAlSzn62ScnPfPnW1YCByKItf0tdP16 teCFmZgR2weR/GmMsCqo5r2U9SPLku8IuSIbTUdJw1TFwoC8GoqQe8aaIZnGuQKydK8gPHNbGbigYwZipwK8rKQDeaVMglpEB7c1g8WFrIN7gr1juArDkdLjqFbWu8cU9j0x3 zmtumR7selFunWSstap6YPoCrnTSo qc/Cm9kzWN7DOFOY3DUcajYhEb 6hHUECOaGtQl5CO31SGezuU8QRxAK4wu1uO4A7fL4VBWdt/Wmo IsEkloMYYt2H/AO1otH8Ihx9k5x61adhoFtaRJLb42TqGUEfVyM4Hwritj7fj7O2pc2RVnZwKFEMPhqvb7qzS/XT9QDTyMLaVfBlYZG3PbtTy6MdkzO7Aqv2R3qG1n9OU j7TFcYVgfs/GuNvvs7oLNQQvaw2VsjTNETEx95DkFScr357YqStSNQtnt0lMXir7koxlD6jNDTqtnYrbCR5j3Lucs1SGlXyxhB9VR9Wpwbf0V3qsFzp rXVpftIZ4nwzSH3m9Dx601nuFKdxRn7V7rS72OJx4kGuWfhrIDGQtxE3kD5leDn4EVWpkkY17NT5RTPHksk9HDSbhitJg3GnMEYIBPepCO3QjIrTCJEMLYoM4Na5OO/FTUygDGKibsDmngkyPk5Y0qywaVIY9y2MYpM5RfjTp1Vaaz4IrnT06E1Fdkhpd5tKqaMtMv1ABJ4qtoJCj5qatNQKL8PvrVdIwfbDDVb9GU4PlQpcxPcMW z2zWMt3JMQq8g leyT HCIt3J745obYRxPskNEfT4pGW6UEepqynYx6RbYOzEKld3BAx/dVMySGMhkYOe444FbNR1TUtR5vL2eY7cAF8D7sDisZVuXk1jZ pB baaaF5GOYnPu48/xNNkiWNzElxDcRgZUwuGA VSlyxt i5F5JSR8k q24/vqstPV42DWjukgHdP51hL0/NeTsdqofjdCPUtW8O4SPd76MV79qlNMv8A3t7uFC5JJ9BQJqsFzd3X0hGCyEDKtwCR5g1ttNSu9NKJfRuuRhS32h/Ol8Zxj0Z/JUmEHtKWR9YspnnEolskZeMFBk8GhqCMHuM1K9XavbarqME1sm0JbJGxJ7kZ5/OoyJhtyK7KlkEclj2TwcohGMCnIcInJpiJiK1zSs3Ga00hozurlRnmo15PEbFZTqSOa0RqVk5p6JI3 HSrcpBGaVSXqMrqTnvTJ5M04vlIpkFJIAGSfKpjBJkybHNlbyXEm1AABy0jHCqPiakms4LVcyTeM48guFrSuLa3WADscufU17ZQXGo362dlE811M22OJO7HGePwBqydPWuCw2jCj0Xite7uKfw9Pa1Ot48Ol3JFk2y5939U2M4P4YP41IydDdUxwvNJotwEVS5JZeFAznv6UgB8kYx5VvsovHvLeI87pVB/EipWbofqdGeM6POXVPEYKykhfI9/gaipYtT0K gW8s5re4bEkKypy/OAQPPnikyoNKSbLI6il8Po1c/65rxx927wh/Cqx24JA4H34qT1DqLV7 2j0ue2kxErKIkhO/BbeSRjPc lRcEGo3Ic29hPOiNtcxRM21vQ4HelGOGt9qnmfkdJeNGAu9mx 9mncWppND4F3CJYQfquMiohkMcpimjkgmX60cilWHpwaxa5aNT4eAoPMjDgU8MCUnsbC5960EkbjyUAj5V6ui3Xhq9vsmBH1VO1v/aajoNSPiBXnUjOMb6fJeSwXajcQFyRzxil/g08G00MsblZI2Rh3VhgitajJ5FEzyDV4SjgG6iXcjftr5qfjUDPF4bnyrJzaeM6a4Ka0bSrzTdkpxI9N3atYsiyviZqOKVYg0qoyM7pgxwPOvLGMeOshGVQ5NaVJdsedPyhgs8qp/SNuzj0piY2lk3hnPqf41LdCgP11oQPY3sdQTnJK TVI9K6rFouvWGqT2zXS2khk8ESbNzYO3nB7Eg9vKkItb2iKB0f1Hr nuY49TFqjKrkESpKySDH3baHPalefQOpXXTtXuluns47e7t1yoRPDXjPnuB5qJvOtRc6Pd6Q lo1hPqf05YnnJ2KWDNHnHILZOf3jTrXeutP1YanKOlbWK/1C3MDXZuC7INoUHBXuAB8qBklrvUdxH7KtNeL3L /zYzXQb3zBDlsZ OcUcR9NR6weidRmO46ZADPuOTygK5z 8Biqc1HqSLUeltM0F9KhjFhLvM6zHdJn6/GON38qM4Pa1p0ZEZ0O ht9sAZUuVY/oie2cdxt VAEh0nMG9rPVeq3zeItnKLZWOOA8ixqPwxWnpO01V4uvNM0fUhp10dWUW8rPhUZpTnHxZQBUZovtA6esLrWbi3sdQin1O/S4Z54kmURhlLDGc5 sR35xWd/wBZ9Nxt1BLpn9avc6jdwXUX6JUVXiKsM5OQCRzQBC 1K5iveqIkS6W6ktbGK2uJkPDTKX3c Z5FbOi7 407o7rKWBwipaxlcqrYd22Z5HocVC9Ua3p qdUS6rYWU8drNIks1vcEAs ffAwTgHGPnU7qGtdIjpzWLDp HUrWTWZIQ8U8SmK2VXDEggngYPHegCwol1a6n0eG60mzm0N9J33ly9shxJsJwG7jyqimuvEQkc8 4T3254Hyq1eodc0fUtP1rSrXqOzNvLpls1rJ4rIBJFkMh LDbx86qBeWXyz5UATum3eyZXDEFTnit tlUmyB7sg3L NQFvMUck9iCOKlJ2kvdHilQFntm2v/ALLdj8x dZzgpGtNnBkfI TxWSRkjOK2WFlJcSDg0UWWgNInY1aWIc7OTBbwx617Rn/o1 7 VKgjUAdum VVJA3MBycUX9ZXlk8FtZ6eqCOIAllbdyBjGe3r86E7TDXkI/fBrffPlseeTWiliaMWtekfMfe48qyXluOxrXKaUD5Xb9ocVBQ9srW4v7qK0s4WmnmbaiL3Jq9ukPZVotrpUf8AXVrDfXj 88kgJVfgo9Pj50D w5Iz1PeNIqkrbLgkdsuAa6AUo QrKcd8GgZU3tU6Q6d0To69utN0m1t7pPDKSxphl/TRqefuY1SL7Qu7OM10h7Zk39B6nxkiIMPwljP8qoroVk/0y0dZEV0NxjawyM4OPzxQAc9D yZdU0wXvUBuYZJQGigjk8Mxqf2uD7x748qJz7FenyPemvyfX6UB/wAlWVAFEKbPqkA8U0l1WzhkMcsmHB5yuKGAAD2K9Oj682okf r/AOiojqj2Sadaaa8ugTXCXiAkLNKXSQY7Hgbfv dWgNd0538NZgW/ZGM/Kn7wq4wTx8KzlKSA4 nBtp5re/jeC4icq6MMEH0IrSrqZBtPFF3tgtlt tpUHCm3jIPpyaB Ff3WqxDhTzRx7MbQard6jpTorrc6fIOTyu11O4fEUCp2qd6S1RNJ1i0up2ZbdiYp2XuqNjJ/Dv8AhTAMtE0cAoWUZxRrp mhU5WsLlbVdVaazH9kuP0kTkYDA9yPhnNTMDARDy4qgGhs48/VpU4kkwxArygDnuxMSCS5lIAjHu5OOTWqWUSkupBHwok9mVgLvqpbmUBobGB52yMgN9VfzP5US9VWen3dw8ghRhkrgrg7vM5rCdqhLDWNTknJFWSede6fbS3D3EiDKwwtK/3L3qY1nQ0tbcyxzHPlGefzqd6I6g0XTOnNV03V7GR57uGWNJo1DHDjGM VXGaktREouL7BrS9W1DSZXm0u9mtJJF2u0LYLD0roL2O6jd6r0pHdajcSXNy0kqtLIcscOcVzVC5CBW4x3roT2DPu6RC/szzf8QqhEx7Xhu6H1Qf VY/JlNc99JyGLqzRXHf6bEvzbH866M9p8Bn6L1NQMk20uB90bH/lrmzp5gvUGkOB2vYD/wDYtIDrawfNjbk9/DT FUT7fbIJ1DYXBA8N7d0yRnDBs/wNXnZ5 gW B/qxn5VS3t8dlvNMYA48SVTn4qhqIvvAAb2eAx9a6WURV3M65A75jauqkG5Fb1ANcl9I8dV6M0bbD9Njw3l3/wAj8a6ngS9NrCVuE/Vr3T4U559gc/8AtutjH1gHzw1uuPwZqAbixnhsre ZT4FwWCNjzU4NHftquJX6uSKYHdDbjB9dzE0wtrj6X0dBp7oGREJU55BJJ fNUvAgPQ8VujbCEevFNgChKkcqcGtimmAb9Iay1pthknPgRr9RjkIPUenxFWhZX4kjHvDGKo7RLGe mAQSLbo6 NKg7KfIfGro0HQbiNN088ZgH6oIT76 RJxx91Q7Yx8mka5S iRxLL78eNp9aVPkFrCux3ckfDtSrn Ub/G/JW/QWjtadOzXbZjlvzkZ/YX6vzJJptryy/o5JZBGSSu1/LHmMetG96FWNEiQJHEuxVxwqjsKFNcuEeKUK/KLjNc9k25nVCpKoCNfv/pDbI 3cn1NQ0EmHI9a3XTFpXySfiaZBiJRivQrgoxPNnJyYu5OPI4q7/6Pl8r2F/Y7hvjl3EZ8mA5/KqRxtmJPAYfnRp7Jdc/qXrK3jcgQ35Fu2f2vs/M8fiKp CToHrGLx nruMjIMbL81I/nXJ lzGC9sJR9iaJvkwNdd6sn0nSp0HO5QR92a5DuYWtZpY//AAZSuM9trEfyoi9A7C047rKL4ZX5HFU9/SEhxDp0mP8AvTDP3xj 6ra0Rs6bGSc5Z f99qrP kGqnRrFxj3btM8 qSj QqV5ApPSZntNWspo TFcxOB6kODXX2nTLJYxtwMArj/ZJH8q5E0uMPq9ijYCm6iGSeCC4rrDT7JRZQ7WYErk59TzRN4gKU9v1usPUNldKV/SwMrf7pBH/FU70h0Bp76HZz3skrSTW6uVB4UkZoc9u5dNetImyUMMp58veA/kKPtG1q3g0Gw8aZFdbZARn90VjfNximdPpq1OTTKU606dOh65cwRyiSMsXXI5waY6dpwuF3yudv7K9/xqe6/1BL/XmmibcAKH4GeOTerEKT5Vo XtKRGRVrj9B50vIn0mCyChIGPO0dzVn2NxbQWQ3OFWL1PlVPaLdp4y5O37vKijUbie6gWRGxD9oKe5FeZZJ6enXBYFjdRW6sQqIR6t3pVT q3c5vX8W4eNv2QewpU1XIl21r6CbqjXZsGKBveJ97b5D76go3e9WCLJMszqoP3nFadXnbeT4mecbcdq39ERvcdU2EZGUWTxDnyCjNa8OtOf3XJ8RxrPs41ezjeaKSOdRknAwaDIbObe/wCicspwfd7V0Hr2pRx25ijYM7cYoASePTZpleNG398irr9U08YrfSrNRWkikblYHIPnVtexzpjROoNK k3lsjX9pd IswZg6lSCvYjI88Gq11h431CV0A2ucjFEPs16uj6N1C8nuIpZYbiFV2x84YHOcZ NdyerThax4dKkKkKwyHJKbcgcVVnXXs30O20PVNRt7ZzeOskokEr4DkZzt3Y7/Ctae27SpLgRzaTd7M/rMr/DNONV9rXTGo6fNZzC8RJo2Rv7MTjIx60sxgGXs71VNa6R068GN7xASD0ccN/8gfnWfV3SVj1VFHb6lkwRssgRWKncNwHIPoxrnXoHrXUOj9RBiLzaZKw8aAny/bXyDfx/Orrj9sHR5QeJqXvef9nl/wANPAGf/ZF0q2VWKXcPSWX/AB1YNjmCBYpXLMpIB2448h3oHPtb6KRyyag249/7PL/hpnf 2PpwRSG0lmmfblQtuwyfvOB JqHy0Ac/pCpbtcaWVZfpBMisvnsIXn5j86roXtzcGGIO5CqAADWnXtcu oNVmvtQY7ycIm4lY18lGf8AJyTU701Z2r6c90GDzIxUgfZ9Pyq/bU8TGrHDwQF2jCU7 9a0O3Ixmn2rECcn40w2SsoYRORngj19K6JQXHDKMnujqGZkfcp59KkG6jubaLZHtBIwQwzQ 7sjEHKsDyD3FayxY5JzmuL4y5azq RJLEOZp3nlaWVyzsck0qbUq6eEf6MG2wm1w7L6RABtDZwamPZ9j u7yXA3RWp2fDJ5pUq81/sZ11/ynuoapdfTZTvHunj4UP397PIzMzcmlSrGtLTpukyFkctKc maQ9KVKvTj4PMfk1yKCe1Yo53bSeKVKqA9ZRuI8qQUelKlTYHu0eleMinypUqAMUCsGBReO2BRp0xCkPT2 MYM0jM/4cCvaVOHkhkDq/6 o4s2Mb2x6bjSpVqyTU/c f30l7UqVSUZUqVKgR//2Q==</t>
+  </si>
+  <si>
+    <t>https://i.pinimg.com/736x/03/79/a8/0379a824c3440eabb14c3c782d424d32.jpg</t>
+  </si>
+  <si>
+    <t>Neymar Jr SS</t>
+  </si>
+  <si>
+    <t>Neymar Jr</t>
   </si>
 </sst>
 </file>
@@ -408,16 +447,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:E34"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="25" customWidth="1"/>
     <col min="2" max="2" width="20" customWidth="1"/>
     <col min="3" max="3" width="30" customWidth="1"/>
     <col min="4" max="4" width="15" customWidth="1"/>
+    <col min="5" max="5" width="50" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -430,23 +470,549 @@
       <c r="D1" t="s">
         <v>3</v>
       </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D2">
-        <v>7</v>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D3">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C5" t="s">
+        <v>7</v>
+      </c>
+      <c r="D5">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C6" t="s">
+        <v>7</v>
+      </c>
+      <c r="D6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>13</v>
+      </c>
+      <c r="B7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C7" t="s">
+        <v>11</v>
+      </c>
+      <c r="D7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8" t="s">
+        <v>6</v>
+      </c>
+      <c r="C8" t="s">
+        <v>7</v>
+      </c>
+      <c r="D8">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>15</v>
+      </c>
+      <c r="B9" t="s">
+        <v>6</v>
+      </c>
+      <c r="C9" t="s">
+        <v>7</v>
+      </c>
+      <c r="D9">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>15</v>
+      </c>
+      <c r="B10" t="s">
+        <v>6</v>
+      </c>
+      <c r="C10" t="s">
+        <v>7</v>
+      </c>
+      <c r="D10">
+        <v>10</v>
+      </c>
+      <c r="E10" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>15</v>
+      </c>
+      <c r="B11" t="s">
+        <v>6</v>
+      </c>
+      <c r="C11" t="s">
+        <v>7</v>
+      </c>
+      <c r="D11">
+        <v>10</v>
+      </c>
+      <c r="E11" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>15</v>
+      </c>
+      <c r="B12" t="s">
+        <v>6</v>
+      </c>
+      <c r="C12" t="s">
+        <v>7</v>
+      </c>
+      <c r="D12">
+        <v>10</v>
+      </c>
+      <c r="E12" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>15</v>
+      </c>
+      <c r="B13" t="s">
+        <v>6</v>
+      </c>
+      <c r="C13" t="s">
+        <v>7</v>
+      </c>
+      <c r="D13">
+        <v>10</v>
+      </c>
+      <c r="E13" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>15</v>
+      </c>
+      <c r="B14" t="s">
+        <v>6</v>
+      </c>
+      <c r="C14" t="s">
+        <v>7</v>
+      </c>
+      <c r="D14">
+        <v>10</v>
+      </c>
+      <c r="E14" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>15</v>
+      </c>
+      <c r="B15" t="s">
+        <v>6</v>
+      </c>
+      <c r="C15" t="s">
+        <v>7</v>
+      </c>
+      <c r="D15">
+        <v>10</v>
+      </c>
+      <c r="E15" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>15</v>
+      </c>
+      <c r="B16" t="s">
+        <v>6</v>
+      </c>
+      <c r="C16" t="s">
+        <v>7</v>
+      </c>
+      <c r="D16">
+        <v>10</v>
+      </c>
+      <c r="E16" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>15</v>
+      </c>
+      <c r="B17" t="s">
+        <v>6</v>
+      </c>
+      <c r="C17" t="s">
+        <v>7</v>
+      </c>
+      <c r="D17">
+        <v>10</v>
+      </c>
+      <c r="E17" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>15</v>
+      </c>
+      <c r="B18" t="s">
+        <v>6</v>
+      </c>
+      <c r="C18" t="s">
+        <v>7</v>
+      </c>
+      <c r="D18">
+        <v>10</v>
+      </c>
+      <c r="E18" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>15</v>
+      </c>
+      <c r="B19" t="s">
+        <v>6</v>
+      </c>
+      <c r="C19" t="s">
+        <v>7</v>
+      </c>
+      <c r="D19">
+        <v>10</v>
+      </c>
+      <c r="E19" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>15</v>
+      </c>
+      <c r="B20" t="s">
+        <v>6</v>
+      </c>
+      <c r="C20" t="s">
+        <v>7</v>
+      </c>
+      <c r="D20">
+        <v>10</v>
+      </c>
+      <c r="E20" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>18</v>
+      </c>
+      <c r="B21" t="s">
+        <v>6</v>
+      </c>
+      <c r="C21" t="s">
+        <v>7</v>
+      </c>
+      <c r="D21">
+        <v>10</v>
+      </c>
+      <c r="E21" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>18</v>
+      </c>
+      <c r="B22" t="s">
+        <v>6</v>
+      </c>
+      <c r="C22" t="s">
+        <v>7</v>
+      </c>
+      <c r="D22">
+        <v>10</v>
+      </c>
+      <c r="E22" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>15</v>
+      </c>
+      <c r="B23" t="s">
+        <v>6</v>
+      </c>
+      <c r="C23" t="s">
+        <v>7</v>
+      </c>
+      <c r="D23">
+        <v>10</v>
+      </c>
+      <c r="E23" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>15</v>
+      </c>
+      <c r="B24" t="s">
+        <v>6</v>
+      </c>
+      <c r="C24" t="s">
+        <v>7</v>
+      </c>
+      <c r="D24">
+        <v>10</v>
+      </c>
+      <c r="E24" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>18</v>
+      </c>
+      <c r="B25" t="s">
+        <v>6</v>
+      </c>
+      <c r="C25" t="s">
+        <v>7</v>
+      </c>
+      <c r="D25">
+        <v>10</v>
+      </c>
+      <c r="E25" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>15</v>
+      </c>
+      <c r="B26" t="s">
+        <v>6</v>
+      </c>
+      <c r="C26" t="s">
+        <v>7</v>
+      </c>
+      <c r="D26">
+        <v>10</v>
+      </c>
+      <c r="E26" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>18</v>
+      </c>
+      <c r="B27" t="s">
+        <v>6</v>
+      </c>
+      <c r="C27" t="s">
+        <v>7</v>
+      </c>
+      <c r="D27">
+        <v>10</v>
+      </c>
+      <c r="E27" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>18</v>
+      </c>
+      <c r="B28" t="s">
+        <v>6</v>
+      </c>
+      <c r="C28" t="s">
+        <v>7</v>
+      </c>
+      <c r="D28">
+        <v>10</v>
+      </c>
+      <c r="E28" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>19</v>
+      </c>
+      <c r="B29" t="s">
+        <v>6</v>
+      </c>
+      <c r="C29" t="s">
+        <v>7</v>
+      </c>
+      <c r="D29">
+        <v>10</v>
+      </c>
+      <c r="E29" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>19</v>
+      </c>
+      <c r="B30" t="s">
+        <v>6</v>
+      </c>
+      <c r="C30" t="s">
+        <v>7</v>
+      </c>
+      <c r="D30">
+        <v>10</v>
+      </c>
+      <c r="E30" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>19</v>
+      </c>
+      <c r="B31" t="s">
+        <v>6</v>
+      </c>
+      <c r="C31" t="s">
+        <v>7</v>
+      </c>
+      <c r="D31">
+        <v>10</v>
+      </c>
+      <c r="E31" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>19</v>
+      </c>
+      <c r="B32" t="s">
+        <v>6</v>
+      </c>
+      <c r="C32" t="s">
+        <v>7</v>
+      </c>
+      <c r="D32">
+        <v>10</v>
+      </c>
+      <c r="E32" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>19</v>
+      </c>
+      <c r="B33" t="s">
+        <v>6</v>
+      </c>
+      <c r="C33" t="s">
+        <v>7</v>
+      </c>
+      <c r="D33">
+        <v>10</v>
+      </c>
+      <c r="E33" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>19</v>
+      </c>
+      <c r="B34" t="s">
+        <v>6</v>
+      </c>
+      <c r="C34" t="s">
+        <v>7</v>
+      </c>
+      <c r="D34">
+        <v>10</v>
+      </c>
+      <c r="E34" t="s">
+        <v>17</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>